--- a/hardware/V1/BOM-PAudio_player-V1.0-260808.xlsx
+++ b/hardware/V1/BOM-PAudio_player-V1.0-260808.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\zhutao\audio_player\hardware\V1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -459,9 +464,6 @@
     <t>U6，U7</t>
   </si>
   <si>
-    <t>MX66100T,C53121238</t>
-  </si>
-  <si>
     <t>音频功放</t>
   </si>
   <si>
@@ -584,20 +586,20 @@
       <t>C</t>
     </r>
   </si>
+  <si>
+    <t>MX66100T,C53121238</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="2">
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -644,113 +646,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="23"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="62"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="63"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="60"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="9"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -763,140 +664,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="55"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="62"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="44"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="30"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="57"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="11"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="36"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="49"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="27"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="51"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="52"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -980,262 +749,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="22"/>
-      </left>
-      <right style="thin">
-        <color indexed="22"/>
-      </right>
-      <top style="thin">
-        <color indexed="22"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="30"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="63"/>
-      </left>
-      <right style="thin">
-        <color indexed="63"/>
-      </right>
-      <top style="thin">
-        <color indexed="63"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="63"/>
-      </left>
-      <right style="double">
-        <color indexed="63"/>
-      </right>
-      <top style="double">
-        <color indexed="63"/>
-      </top>
-      <bottom style="double">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="52"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="62"/>
-      </top>
-      <bottom style="double">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1255,11 +771,131 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1267,188 +903,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FF0000"/>
-      <color rgb="00000000"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1735,18 +1207,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
-    <col min="2" max="2" width="27.6" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.7416666666667" style="4" customWidth="1"/>
+    <col min="2" max="2" width="27.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.75" style="4" customWidth="1"/>
     <col min="4" max="4" width="12" style="4" customWidth="1"/>
     <col min="5" max="5" width="9" style="5"/>
     <col min="6" max="6" width="8.5" style="6" customWidth="1"/>
@@ -1757,1263 +1229,1263 @@
     <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="37.5" customHeight="1" spans="1:12">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-    </row>
-    <row r="2" ht="20.25" spans="1:12">
-      <c r="A2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+    </row>
+    <row r="2" spans="1:12" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17">
-        <v>1</v>
-      </c>
-      <c r="F3" s="18">
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15">
+        <v>1</v>
+      </c>
+      <c r="F3" s="16">
         <v>10</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="17">
         <f t="shared" ref="G3:G9" si="0">E3*F3</f>
         <v>10</v>
       </c>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="14" t="s">
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17">
-        <v>1</v>
-      </c>
-      <c r="F4" s="18">
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
         <v>10</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="14" t="s">
+      <c r="H4" s="13"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18">
+      <c r="C5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="15">
+        <v>1</v>
+      </c>
+      <c r="F5" s="16">
         <v>3</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="14" t="s">
+      <c r="H5" s="13"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17">
-        <v>1</v>
-      </c>
-      <c r="F6" s="18">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16">
         <v>23</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="14" t="s">
+      <c r="H6" s="13"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17">
-        <v>1</v>
-      </c>
-      <c r="F7" s="18">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15">
+        <v>1</v>
+      </c>
+      <c r="F7" s="16">
         <v>10</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="14" t="s">
+      <c r="H7" s="13"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16">
         <v>10</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="54" spans="1:12">
-      <c r="A9" s="21" t="s">
+      <c r="H8" s="13"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="54" x14ac:dyDescent="0.15">
+      <c r="A9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <v>26</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="23">
         <v>0.06</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="19">
         <f t="shared" si="0"/>
         <v>1.56</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="40.5" spans="1:12">
-      <c r="A10" s="21" t="s">
+      <c r="H9" s="19"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+    </row>
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <v>16</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="23">
         <v>0.06</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="19">
         <f t="shared" ref="G10:G15" si="1">E10*F10</f>
         <v>0.96</v>
       </c>
-      <c r="H10" s="22"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="26"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:12">
-      <c r="A11" s="21" t="s">
+      <c r="H10" s="20"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="24"/>
+    </row>
+    <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <v>2</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="23">
         <v>0.2</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="19">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
-      <c r="H11" s="22"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="26"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="27" spans="1:12">
-      <c r="A12" s="22" t="s">
+      <c r="H11" s="20"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="24"/>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="29">
-        <v>1</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="E12" s="27">
+        <v>1</v>
+      </c>
+      <c r="F12" s="28">
         <v>0.2</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="20">
         <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="27"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="40.5" spans="1:12">
-      <c r="A13" s="21" t="s">
+      <c r="H12" s="20"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <v>17</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="23">
         <v>0.01</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="19">
         <f t="shared" si="1"/>
         <v>0.17</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="26"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:12">
-      <c r="A14" s="21" t="s">
+      <c r="H13" s="19"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="24"/>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="24">
-        <v>1</v>
-      </c>
-      <c r="F14" s="25">
+      <c r="E14" s="22">
+        <v>1</v>
+      </c>
+      <c r="F14" s="23">
         <v>0.01</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="19">
         <f t="shared" si="1"/>
         <v>0.01</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="26"/>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="1:12">
-      <c r="A15" s="21" t="s">
+      <c r="H14" s="19"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="24"/>
+    </row>
+    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="24">
-        <v>1</v>
-      </c>
-      <c r="F15" s="25">
+      <c r="E15" s="22">
+        <v>1</v>
+      </c>
+      <c r="F15" s="23">
         <v>0.01</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="19">
         <f t="shared" si="1"/>
         <v>0.01</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="26"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:12">
-      <c r="A16" s="21" t="s">
+      <c r="H15" s="19"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="24"/>
+    </row>
+    <row r="16" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="24">
-        <v>1</v>
-      </c>
-      <c r="F16" s="25">
+      <c r="E16" s="22">
+        <v>1</v>
+      </c>
+      <c r="F16" s="23">
         <v>0.01</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="19">
         <f t="shared" ref="G16:G28" si="2">E16*F16</f>
         <v>0.01</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="26"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:12">
-      <c r="A17" s="21" t="s">
+      <c r="H16" s="19"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="24"/>
+    </row>
+    <row r="17" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="22">
         <v>2</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <v>0.01</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="19">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="26"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:12">
-      <c r="A18" s="21" t="s">
+      <c r="H17" s="19"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="24"/>
+    </row>
+    <row r="18" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="22">
         <v>3</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="23">
         <v>0.01</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="19">
         <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="26"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="40.5" spans="1:12">
-      <c r="A19" s="21" t="s">
+      <c r="H18" s="19"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="24"/>
+    </row>
+    <row r="19" spans="1:12" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A19" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="22">
         <v>16</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="23">
         <v>0.01</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="19">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="26"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:12">
-      <c r="A20" s="21" t="s">
+      <c r="H19" s="19"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="24"/>
+    </row>
+    <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="22">
         <v>2</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="23">
         <v>0.01</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="19">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="H20" s="21"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="26"/>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:12">
-      <c r="A21" s="32" t="s">
+      <c r="H20" s="19"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="24"/>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="32">
         <v>2</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="23">
         <v>0.01</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="19">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:12">
-      <c r="A22" s="32" t="s">
+    <row r="22" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="32">
         <v>2</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="23">
         <v>0.01</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="19">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="1:12">
-      <c r="A23" s="21" t="s">
+    <row r="23" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="22">
         <v>6</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="23">
         <v>0.01</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="19">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:12">
-      <c r="A24" s="22" t="s">
+      <c r="H23" s="19"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+    </row>
+    <row r="24" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="22">
         <v>4</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="23">
         <v>0.1</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="19">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="H24" s="21"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="26"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A25" s="22" t="s">
+      <c r="H24" s="19"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A25" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="22">
         <v>2</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="23">
         <v>0.22</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="19">
         <f t="shared" si="2"/>
         <v>0.44</v>
       </c>
-      <c r="H25" s="21"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A26" s="22" t="s">
+      <c r="H25" s="19"/>
+    </row>
+    <row r="26" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A26" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="22">
         <v>3</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="23">
         <v>0.1</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="19">
         <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
-      <c r="H26" s="21"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A27" s="35" t="s">
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A27" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="22">
         <v>2</v>
       </c>
-      <c r="F27" s="25">
-        <v>0.07</v>
-      </c>
-      <c r="G27" s="21">
+      <c r="F27" s="23">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G27" s="19">
         <f t="shared" si="2"/>
-        <v>0.14</v>
-      </c>
-      <c r="H27" s="21"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A28" s="35" t="s">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H27" s="19"/>
+    </row>
+    <row r="28" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A28" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="24">
-        <v>1</v>
-      </c>
-      <c r="F28" s="25">
+      <c r="E28" s="22">
+        <v>1</v>
+      </c>
+      <c r="F28" s="23">
         <v>0.18</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="19">
         <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
-      <c r="H28" s="21"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A29" s="35" t="s">
+      <c r="H28" s="19"/>
+    </row>
+    <row r="29" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A29" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="37">
-        <v>1</v>
-      </c>
-      <c r="F29" s="38">
+      <c r="E29" s="35">
+        <v>1</v>
+      </c>
+      <c r="F29" s="36">
         <v>0.3</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="36">
         <f>F29*E29</f>
         <v>0.3</v>
       </c>
-      <c r="H29" s="39"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:12">
-      <c r="A30" s="35" t="s">
+      <c r="H29" s="37"/>
+    </row>
+    <row r="30" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="22">
         <v>3</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="23">
         <v>0.1</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="19">
         <f t="shared" ref="G30:G49" si="3">E30*F30</f>
         <v>0.3</v>
       </c>
-      <c r="H30" s="21"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:12">
-      <c r="A31" s="35" t="s">
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="22">
         <v>4</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="23">
         <v>0.6</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="19">
         <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
-      <c r="H31" s="21"/>
-    </row>
-    <row r="32" s="3" customFormat="1" ht="27" spans="1:12">
-      <c r="A32" s="22" t="s">
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" spans="1:12" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A32" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="24">
-        <v>1</v>
-      </c>
-      <c r="F32" s="25">
+      <c r="E32" s="22">
+        <v>1</v>
+      </c>
+      <c r="F32" s="23">
         <v>0.7</v>
       </c>
-      <c r="G32" s="21">
+      <c r="G32" s="19">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="H32" s="21"/>
+      <c r="H32" s="19"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" s="3" customFormat="1" ht="27" spans="1:12">
-      <c r="A33" s="22" t="s">
+    <row r="33" spans="1:12" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A33" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="24">
-        <v>1</v>
-      </c>
-      <c r="F33" s="25">
+      <c r="E33" s="22">
+        <v>1</v>
+      </c>
+      <c r="F33" s="23">
         <v>0.4</v>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="19">
         <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
-      <c r="H33" s="21"/>
+      <c r="H33" s="19"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A34" s="40" t="s">
+    <row r="34" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A34" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="41">
-        <v>1</v>
-      </c>
-      <c r="F34" s="22">
+      <c r="E34" s="39">
+        <v>1</v>
+      </c>
+      <c r="F34" s="20">
         <v>32</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="19">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="H34" s="39"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A35" s="42" t="s">
+      <c r="H34" s="37"/>
+    </row>
+    <row r="35" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A35" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="24">
-        <v>1</v>
-      </c>
-      <c r="F35" s="43">
+      <c r="E35" s="22">
+        <v>1</v>
+      </c>
+      <c r="F35" s="41">
         <v>0.52</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="19">
         <f t="shared" si="3"/>
         <v>0.52</v>
       </c>
-      <c r="H35" s="44"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:12">
-      <c r="A36" s="22" t="s">
+      <c r="H35" s="42"/>
+    </row>
+    <row r="36" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="24">
-        <v>1</v>
-      </c>
-      <c r="F36" s="25">
+      <c r="E36" s="22">
+        <v>1</v>
+      </c>
+      <c r="F36" s="23">
         <v>0.92</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="19">
         <f t="shared" si="3"/>
         <v>0.92</v>
       </c>
-      <c r="H36" s="21"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:12">
-      <c r="A37" s="22" t="s">
+      <c r="H36" s="19"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+    </row>
+    <row r="37" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="24">
-        <v>1</v>
-      </c>
-      <c r="F37" s="25">
+      <c r="E37" s="22">
+        <v>1</v>
+      </c>
+      <c r="F37" s="23">
         <v>0.4</v>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="19">
         <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
-      <c r="H37" s="21"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:12">
-      <c r="A38" s="21" t="s">
+      <c r="H37" s="19"/>
+    </row>
+    <row r="38" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E38" s="41">
-        <v>1</v>
-      </c>
-      <c r="F38" s="25">
+      <c r="E38" s="39">
+        <v>1</v>
+      </c>
+      <c r="F38" s="23">
         <v>0.8</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="19">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="H38" s="21"/>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A39" s="45" t="s">
+      <c r="H38" s="19"/>
+    </row>
+    <row r="39" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A39" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C39" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="22" t="s">
+      <c r="C39" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="22">
         <v>2</v>
       </c>
-      <c r="F39" s="43">
+      <c r="F39" s="41">
         <v>0.7</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="19">
         <f t="shared" si="3"/>
         <v>1.4</v>
       </c>
-      <c r="H39" s="39"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:12">
-      <c r="A40" s="28" t="s">
+      <c r="H39" s="37"/>
+    </row>
+    <row r="40" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="C40" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="D40" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="E40" s="22">
+        <v>1</v>
+      </c>
+      <c r="F40" s="19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G40" s="19">
+        <f t="shared" si="3"/>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H40" s="44"/>
+    </row>
+    <row r="41" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="24">
-        <v>1</v>
-      </c>
-      <c r="F40" s="21">
-        <v>8.2</v>
-      </c>
-      <c r="G40" s="21">
-        <f t="shared" si="3"/>
-        <v>8.2</v>
-      </c>
-      <c r="H40" s="46"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:12">
-      <c r="A41" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="22" t="s">
+      <c r="C41" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="35" t="s">
+      <c r="D41" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="41">
-        <v>1</v>
-      </c>
-      <c r="F41" s="22">
+      <c r="E41" s="39">
+        <v>1</v>
+      </c>
+      <c r="F41" s="20">
         <v>0.4</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41" s="19">
         <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
-      <c r="H41" s="39"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:12">
-      <c r="A42" s="45" t="s">
+      <c r="H41" s="37"/>
+    </row>
+    <row r="42" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="C42" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" s="24">
-        <v>1</v>
-      </c>
-      <c r="F42" s="47">
+      <c r="D42" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42" s="22">
+        <v>1</v>
+      </c>
+      <c r="F42" s="45">
         <v>0.8</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="19">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="H42" s="39"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A43" s="48" t="s">
+      <c r="H42" s="37"/>
+    </row>
+    <row r="43" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A43" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="36" t="s">
+      <c r="C43" s="33" t="s">
         <v>121</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>122</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E43" s="41">
-        <v>1</v>
-      </c>
-      <c r="F43" s="47">
-        <v>1.1</v>
-      </c>
-      <c r="G43" s="21">
+      <c r="E43" s="39">
+        <v>1</v>
+      </c>
+      <c r="F43" s="45">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G43" s="19">
         <f t="shared" si="3"/>
-        <v>1.1</v>
-      </c>
-      <c r="H43" s="39"/>
-    </row>
-    <row r="44" s="3" customFormat="1" ht="27" spans="1:12">
-      <c r="A44" s="45" t="s">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H43" s="37"/>
+    </row>
+    <row r="44" spans="1:12" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A44" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="C44" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="C44" s="35" t="s">
+      <c r="D44" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" s="24">
-        <v>1</v>
-      </c>
-      <c r="F44" s="47">
+      <c r="E44" s="22">
+        <v>1</v>
+      </c>
+      <c r="F44" s="45">
         <v>0.91</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="19">
         <f t="shared" si="3"/>
         <v>0.91</v>
       </c>
-      <c r="H44" s="39"/>
-    </row>
-    <row r="45" s="3" customFormat="1" ht="40.5" spans="1:12">
-      <c r="A45" s="45" t="s">
+      <c r="H44" s="37"/>
+    </row>
+    <row r="45" spans="1:12" s="3" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A45" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="C45" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="C45" s="35" t="s">
+      <c r="D45" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="24">
+      <c r="E45" s="22">
         <v>6</v>
       </c>
-      <c r="F45" s="47">
+      <c r="F45" s="45">
         <v>0.87</v>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="19">
         <f t="shared" si="3"/>
         <v>5.22</v>
       </c>
-      <c r="H45" s="39"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A46" s="35" t="s">
+      <c r="H45" s="37"/>
+    </row>
+    <row r="46" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A46" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="C46" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="35" t="s">
+      <c r="D46" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="24">
+      <c r="E46" s="22">
         <v>2</v>
       </c>
-      <c r="F46" s="25">
+      <c r="F46" s="23">
         <v>0.3</v>
       </c>
-      <c r="G46" s="21">
+      <c r="G46" s="19">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
-      <c r="H46" s="21"/>
-    </row>
-    <row r="47" s="3" customFormat="1" ht="27" spans="1:12">
-      <c r="A47" s="45" t="s">
+      <c r="H46" s="19"/>
+    </row>
+    <row r="47" spans="1:12" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A47" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="C47" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="28" t="s">
+      <c r="D47" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="24">
-        <v>1</v>
-      </c>
-      <c r="F47" s="47">
+      <c r="E47" s="22">
+        <v>1</v>
+      </c>
+      <c r="F47" s="45">
         <v>0.52</v>
       </c>
-      <c r="G47" s="21">
+      <c r="G47" s="19">
         <f t="shared" si="3"/>
         <v>0.52</v>
       </c>
-      <c r="H47" s="39"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="27" spans="1:12">
-      <c r="A48" s="22" t="s">
+      <c r="H47" s="37"/>
+    </row>
+    <row r="48" spans="1:12" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A48" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B48" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="C48" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="D48" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" s="24">
-        <v>1</v>
-      </c>
-      <c r="F48" s="22">
+      <c r="E48" s="22">
+        <v>1</v>
+      </c>
+      <c r="F48" s="20">
         <v>0.1</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="19">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="H48" s="22"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="27" spans="1:8">
-      <c r="A49" s="22" t="s">
+      <c r="H48" s="20"/>
+    </row>
+    <row r="49" spans="1:8" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A49" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B49" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="C49" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="22"/>
-      <c r="E49" s="24">
+      <c r="D49" s="20"/>
+      <c r="E49" s="22">
         <v>12</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="20">
         <v>0</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H49" s="22"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="G50" s="4">
         <f>SUM(G3:G46)</f>
-        <v>128.48</v>
+        <v>128.47999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="600"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300"/>
 </worksheet>
 </file>